--- a/summary output/summary cafri 6_6 23sept2025.xlsx
+++ b/summary output/summary cafri 6_6 23sept2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pjs23\Documents\R\slash-wall-vegetation\summary output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CA68B3C-6E56-49D7-8B0E-DEF7C0B36BD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC9F5663-C2EB-4868-AE41-774EAB82714E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="88">
   <si>
     <t>filename</t>
   </si>
@@ -196,25 +196,7 @@
     <t>other</t>
   </si>
   <si>
-    <t>richness_all_sizes</t>
-  </si>
-  <si>
-    <t>richness_GTR1ft</t>
-  </si>
-  <si>
-    <t>richness_GTR5ft</t>
-  </si>
-  <si>
     <t>occup_any_count</t>
-  </si>
-  <si>
-    <t>occup_any_pct</t>
-  </si>
-  <si>
-    <t>occup_GTR1ft_pct</t>
-  </si>
-  <si>
-    <t>occup_GTR5ft_pct</t>
   </si>
   <si>
     <t>occup_GTR1ft_count</t>
@@ -241,26 +223,77 @@
     <t>TOTAL</t>
   </si>
   <si>
-    <t>Occupancy of species-type by treatment and brushing</t>
-  </si>
-  <si>
     <t>final_result</t>
   </si>
   <si>
-    <t># seasons</t>
+    <t>forest_type_occupancy</t>
   </si>
   <si>
-    <t>Top 5 Species in CAFRI 6_6 after 3 Growing Seasons</t>
+    <t>richness_all_sizes (# of woody spp)</t>
   </si>
   <si>
-    <t>forest_type_occupancy</t>
+    <t>richness_GTR1ft  (# of woody spp)</t>
+  </si>
+  <si>
+    <t>richness_GTR5ft  (# of woody spp)</t>
+  </si>
+  <si>
+    <t>growing seasons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% Points Occupied (any size) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">% Points Occupied (GTR 1 ft) </t>
+  </si>
+  <si>
+    <t>% Points Occupied (GTR 5 ft)</t>
+  </si>
+  <si>
+    <t># Woody Species by Treatment and Brushing for CAFRI 6_6</t>
+  </si>
+  <si>
+    <t>all_sizes (stems/acre)</t>
+  </si>
+  <si>
+    <t>GTR 1 ft tall (stems/acre)</t>
+  </si>
+  <si>
+    <t>GTR 5 ft (stems/acre)</t>
+  </si>
+  <si>
+    <t>GTR 5 ft exposed (stems/acre)</t>
+  </si>
+  <si>
+    <t># growing seasons</t>
+  </si>
+  <si>
+    <t>ab, eh, rm, stm, svb, wh</t>
+  </si>
+  <si>
+    <t>ab, bc, bta, eh, pc, qa, rm, sb, sm, smc, stm, wi, yb</t>
+  </si>
+  <si>
+    <t>ab, bta, eh, he, rm, sb, sm, stm, wh</t>
+  </si>
+  <si>
+    <t>ab, bta, eh, pc, rm, sb, sm, stm, yb</t>
+  </si>
+  <si>
+    <t>Species Present &gt; 5 ft Tall</t>
+  </si>
+  <si>
+    <t>% Sample Points Occupied by Species-Type by Treatment and Brushing</t>
+  </si>
+  <si>
+    <t>Top 5 Species (GTR 1 ft) in CAFRI 6_6 after 3 Growing Seasons</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -271,13 +304,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -306,7 +332,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -329,11 +355,168 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -348,25 +531,84 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -668,16 +910,16 @@
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.5703125" customWidth="1"/>
-    <col min="3" max="3" width="4.140625" style="8" customWidth="1"/>
-    <col min="4" max="5" width="11.42578125" style="8"/>
-    <col min="6" max="6" width="6.28515625" style="8" customWidth="1"/>
-    <col min="7" max="10" width="8.5703125" style="8" customWidth="1"/>
-    <col min="11" max="20" width="0" style="8" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="4.140625" style="6" customWidth="1"/>
+    <col min="4" max="5" width="11.42578125" style="6"/>
+    <col min="6" max="6" width="6.28515625" style="6" customWidth="1"/>
+    <col min="7" max="10" width="8.5703125" style="6" customWidth="1"/>
+    <col min="11" max="20" width="0" style="6" hidden="1" customWidth="1"/>
     <col min="21" max="21" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -685,23 +927,23 @@
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>67</v>
+      <c r="A3" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B4" t="s">
@@ -709,20 +951,19 @@
       </c>
     </row>
     <row r="6" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B6" s="10"/>
-      <c r="D6" s="11" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="B6" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" ht="147" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="9" t="s">
-        <v>74</v>
+      <c r="C7" s="7" t="s">
+        <v>80</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>7</v>
@@ -730,50 +971,50 @@
       <c r="E7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="J7" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="K7" s="8" t="s">
+      <c r="G7" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="K7" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="L7" s="8" t="s">
+      <c r="L7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="M7" s="8" t="s">
+      <c r="M7" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="N7" s="8" t="s">
+      <c r="N7" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="O7" s="8" t="s">
+      <c r="O7" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="P7" s="8" t="s">
+      <c r="P7" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="Q7" s="8" t="s">
+      <c r="Q7" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="R7" s="8" t="s">
+      <c r="R7" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="S7" s="8" t="s">
+      <c r="S7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="T7" s="8" t="s">
-        <v>68</v>
+      <c r="T7" s="6" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -807,34 +1048,34 @@
       <c r="J8" s="2">
         <v>600</v>
       </c>
-      <c r="K8" s="8">
+      <c r="K8" s="6">
         <v>2850</v>
       </c>
-      <c r="L8" s="8">
-        <v>0</v>
-      </c>
-      <c r="M8" s="8">
+      <c r="L8" s="6">
+        <v>0</v>
+      </c>
+      <c r="M8" s="6">
         <v>867</v>
       </c>
-      <c r="N8" s="8">
+      <c r="N8" s="6">
         <v>96</v>
       </c>
-      <c r="O8" s="8">
-        <v>3</v>
-      </c>
-      <c r="P8" s="8">
+      <c r="O8" s="6">
+        <v>3</v>
+      </c>
+      <c r="P8" s="6">
         <v>16966</v>
       </c>
-      <c r="Q8" s="8">
+      <c r="Q8" s="6">
         <v>597</v>
       </c>
-      <c r="R8" s="8">
-        <v>3</v>
-      </c>
-      <c r="S8" s="8">
+      <c r="R8" s="6">
+        <v>3</v>
+      </c>
+      <c r="S8" s="6">
         <v>5</v>
       </c>
-      <c r="T8" s="8">
+      <c r="T8" s="6">
         <v>1</v>
       </c>
     </row>
@@ -851,7 +1092,7 @@
       <c r="D9" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="9" t="s">
         <v>30</v>
       </c>
       <c r="F9" s="2">
@@ -863,40 +1104,40 @@
       <c r="H9" s="2">
         <v>1515</v>
       </c>
-      <c r="I9" s="12">
+      <c r="I9" s="9">
         <v>784</v>
       </c>
       <c r="J9" s="2">
         <v>767</v>
       </c>
-      <c r="K9" s="8">
+      <c r="K9" s="6">
         <v>58</v>
       </c>
-      <c r="L9" s="8">
+      <c r="L9" s="6">
         <v>1215</v>
       </c>
-      <c r="M9" s="8">
-        <v>0</v>
-      </c>
-      <c r="N9" s="8">
-        <v>0</v>
-      </c>
-      <c r="O9" s="8">
+      <c r="M9" s="6">
+        <v>0</v>
+      </c>
+      <c r="N9" s="6">
+        <v>0</v>
+      </c>
+      <c r="O9" s="6">
         <v>16</v>
       </c>
-      <c r="P9" s="8">
+      <c r="P9" s="6">
         <v>732</v>
       </c>
-      <c r="Q9" s="8">
+      <c r="Q9" s="6">
         <v>751</v>
       </c>
-      <c r="R9" s="8">
+      <c r="R9" s="6">
         <v>16</v>
       </c>
-      <c r="S9" s="8">
+      <c r="S9" s="6">
         <v>2</v>
       </c>
-      <c r="T9" s="8">
+      <c r="T9" s="6">
         <v>2</v>
       </c>
     </row>
@@ -931,34 +1172,34 @@
       <c r="J10" s="2">
         <v>0</v>
       </c>
-      <c r="K10" s="8">
+      <c r="K10" s="6">
         <v>58</v>
       </c>
-      <c r="L10" s="8">
+      <c r="L10" s="6">
         <v>51</v>
       </c>
-      <c r="M10" s="8">
-        <v>0</v>
-      </c>
-      <c r="N10" s="8">
-        <v>0</v>
-      </c>
-      <c r="O10" s="8">
-        <v>0</v>
-      </c>
-      <c r="P10" s="8">
+      <c r="M10" s="6">
+        <v>0</v>
+      </c>
+      <c r="N10" s="6">
+        <v>0</v>
+      </c>
+      <c r="O10" s="6">
+        <v>0</v>
+      </c>
+      <c r="P10" s="6">
         <v>1348</v>
       </c>
-      <c r="Q10" s="8">
-        <v>0</v>
-      </c>
-      <c r="R10" s="8">
-        <v>0</v>
-      </c>
-      <c r="S10" s="8">
-        <v>0</v>
-      </c>
-      <c r="T10" s="8">
+      <c r="Q10" s="6">
+        <v>0</v>
+      </c>
+      <c r="R10" s="6">
+        <v>0</v>
+      </c>
+      <c r="S10" s="6">
+        <v>0</v>
+      </c>
+      <c r="T10" s="6">
         <v>3</v>
       </c>
     </row>
@@ -993,34 +1234,34 @@
       <c r="J11" s="2">
         <v>366</v>
       </c>
-      <c r="K11" s="8">
+      <c r="K11" s="6">
         <v>116</v>
       </c>
-      <c r="L11" s="8">
-        <v>0</v>
-      </c>
-      <c r="M11" s="8">
+      <c r="L11" s="6">
+        <v>0</v>
+      </c>
+      <c r="M11" s="6">
         <v>19</v>
       </c>
-      <c r="N11" s="8">
-        <v>0</v>
-      </c>
-      <c r="O11" s="8">
-        <v>0</v>
-      </c>
-      <c r="P11" s="8">
+      <c r="N11" s="6">
+        <v>0</v>
+      </c>
+      <c r="O11" s="6">
+        <v>0</v>
+      </c>
+      <c r="P11" s="6">
         <v>847</v>
       </c>
-      <c r="Q11" s="8">
+      <c r="Q11" s="6">
         <v>366</v>
       </c>
-      <c r="R11" s="8">
-        <v>0</v>
-      </c>
-      <c r="S11" s="8">
+      <c r="R11" s="6">
+        <v>0</v>
+      </c>
+      <c r="S11" s="6">
         <v>2</v>
       </c>
-      <c r="T11" s="8">
+      <c r="T11" s="6">
         <v>4</v>
       </c>
     </row>
@@ -1055,34 +1296,34 @@
       <c r="J12" s="2">
         <v>22</v>
       </c>
-      <c r="K12" s="8">
+      <c r="K12" s="6">
         <v>77</v>
       </c>
-      <c r="L12" s="8">
-        <v>0</v>
-      </c>
-      <c r="M12" s="8">
-        <v>0</v>
-      </c>
-      <c r="N12" s="8">
-        <v>0</v>
-      </c>
-      <c r="O12" s="8">
-        <v>3</v>
-      </c>
-      <c r="P12" s="8">
+      <c r="L12" s="6">
+        <v>0</v>
+      </c>
+      <c r="M12" s="6">
+        <v>0</v>
+      </c>
+      <c r="N12" s="6">
+        <v>0</v>
+      </c>
+      <c r="O12" s="6">
+        <v>3</v>
+      </c>
+      <c r="P12" s="6">
         <v>924</v>
       </c>
-      <c r="Q12" s="8">
+      <c r="Q12" s="6">
         <v>19</v>
       </c>
-      <c r="R12" s="8">
-        <v>3</v>
-      </c>
-      <c r="S12" s="8">
-        <v>0</v>
-      </c>
-      <c r="T12" s="8">
+      <c r="R12" s="6">
+        <v>3</v>
+      </c>
+      <c r="S12" s="6">
+        <v>0</v>
+      </c>
+      <c r="T12" s="6">
         <v>5</v>
       </c>
     </row>
@@ -1097,7 +1338,7 @@
         <v>3</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
@@ -1113,34 +1354,34 @@
       <c r="J13" s="2">
         <v>0</v>
       </c>
-      <c r="K13" s="8">
+      <c r="K13" s="6">
         <v>90</v>
       </c>
-      <c r="L13" s="8">
+      <c r="L13" s="6">
         <v>5671</v>
       </c>
-      <c r="M13" s="8">
+      <c r="M13" s="6">
         <v>19</v>
       </c>
-      <c r="N13" s="8">
-        <v>0</v>
-      </c>
-      <c r="O13" s="8">
-        <v>0</v>
-      </c>
-      <c r="P13" s="8">
+      <c r="N13" s="6">
+        <v>0</v>
+      </c>
+      <c r="O13" s="6">
+        <v>0</v>
+      </c>
+      <c r="P13" s="6">
         <v>577</v>
       </c>
-      <c r="Q13" s="8">
-        <v>0</v>
-      </c>
-      <c r="R13" s="8">
-        <v>0</v>
-      </c>
-      <c r="S13" s="8">
+      <c r="Q13" s="6">
+        <v>0</v>
+      </c>
+      <c r="R13" s="6">
+        <v>0</v>
+      </c>
+      <c r="S13" s="6">
         <v>2</v>
       </c>
-      <c r="T13" s="8">
+      <c r="T13" s="6">
         <v>6</v>
       </c>
     </row>
@@ -1155,7 +1396,7 @@
         <v>3</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
@@ -1171,34 +1412,34 @@
       <c r="J14" s="2">
         <v>1755</v>
       </c>
-      <c r="K14" s="8">
+      <c r="K14" s="6">
         <v>3249</v>
       </c>
-      <c r="L14" s="8">
+      <c r="L14" s="6">
         <v>6937</v>
       </c>
-      <c r="M14" s="8">
+      <c r="M14" s="6">
         <v>905</v>
       </c>
-      <c r="N14" s="8">
+      <c r="N14" s="6">
         <v>96</v>
       </c>
-      <c r="O14" s="8">
+      <c r="O14" s="6">
         <v>22</v>
       </c>
-      <c r="P14" s="8">
+      <c r="P14" s="6">
         <v>21394</v>
       </c>
-      <c r="Q14" s="8">
+      <c r="Q14" s="6">
         <v>1733</v>
       </c>
-      <c r="R14" s="8">
+      <c r="R14" s="6">
         <v>22</v>
       </c>
-      <c r="S14" s="8">
+      <c r="S14" s="6">
         <v>11</v>
       </c>
-      <c r="T14" s="8">
+      <c r="T14" s="6">
         <v>7</v>
       </c>
     </row>
@@ -1213,7 +1454,7 @@
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
-      <c r="T15" s="8">
+      <c r="T15" s="6">
         <v>8</v>
       </c>
     </row>
@@ -1248,34 +1489,34 @@
       <c r="J16" s="2">
         <v>1058</v>
       </c>
-      <c r="K16" s="8">
+      <c r="K16" s="6">
         <v>886</v>
       </c>
-      <c r="L16" s="8">
-        <v>0</v>
-      </c>
-      <c r="M16" s="8">
+      <c r="L16" s="6">
+        <v>0</v>
+      </c>
+      <c r="M16" s="6">
         <v>501</v>
       </c>
-      <c r="N16" s="8">
-        <v>0</v>
-      </c>
-      <c r="O16" s="8">
+      <c r="N16" s="6">
+        <v>0</v>
+      </c>
+      <c r="O16" s="6">
         <v>268</v>
       </c>
-      <c r="P16" s="8">
+      <c r="P16" s="6">
         <v>3486</v>
       </c>
-      <c r="Q16" s="8">
+      <c r="Q16" s="6">
         <v>790</v>
       </c>
-      <c r="R16" s="8">
+      <c r="R16" s="6">
         <v>268</v>
       </c>
-      <c r="S16" s="8">
+      <c r="S16" s="6">
         <v>2</v>
       </c>
-      <c r="T16" s="8">
+      <c r="T16" s="6">
         <v>1</v>
       </c>
     </row>
@@ -1310,34 +1551,34 @@
       <c r="J17" s="2">
         <v>22</v>
       </c>
-      <c r="K17" s="8">
-        <v>0</v>
-      </c>
-      <c r="L17" s="8">
+      <c r="K17" s="6">
+        <v>0</v>
+      </c>
+      <c r="L17" s="6">
         <v>203</v>
       </c>
-      <c r="M17" s="8">
+      <c r="M17" s="6">
         <v>19</v>
       </c>
-      <c r="N17" s="8">
-        <v>0</v>
-      </c>
-      <c r="O17" s="8">
-        <v>3</v>
-      </c>
-      <c r="P17" s="8">
+      <c r="N17" s="6">
+        <v>0</v>
+      </c>
+      <c r="O17" s="6">
+        <v>3</v>
+      </c>
+      <c r="P17" s="6">
         <v>578</v>
       </c>
-      <c r="Q17" s="8">
+      <c r="Q17" s="6">
         <v>19</v>
       </c>
-      <c r="R17" s="8">
-        <v>3</v>
-      </c>
-      <c r="S17" s="8">
-        <v>0</v>
-      </c>
-      <c r="T17" s="8">
+      <c r="R17" s="6">
+        <v>3</v>
+      </c>
+      <c r="S17" s="6">
+        <v>0</v>
+      </c>
+      <c r="T17" s="6">
         <v>2</v>
       </c>
     </row>
@@ -1372,34 +1613,34 @@
       <c r="J18" s="2">
         <v>175</v>
       </c>
-      <c r="K18" s="8">
-        <v>0</v>
-      </c>
-      <c r="L18" s="8">
-        <v>0</v>
-      </c>
-      <c r="M18" s="8">
-        <v>0</v>
-      </c>
-      <c r="N18" s="8">
-        <v>0</v>
-      </c>
-      <c r="O18" s="8">
+      <c r="K18" s="6">
+        <v>0</v>
+      </c>
+      <c r="L18" s="6">
+        <v>0</v>
+      </c>
+      <c r="M18" s="6">
+        <v>0</v>
+      </c>
+      <c r="N18" s="6">
+        <v>0</v>
+      </c>
+      <c r="O18" s="6">
         <v>60</v>
       </c>
-      <c r="P18" s="8">
+      <c r="P18" s="6">
         <v>193</v>
       </c>
-      <c r="Q18" s="8">
+      <c r="Q18" s="6">
         <v>116</v>
       </c>
-      <c r="R18" s="8">
+      <c r="R18" s="6">
         <v>60</v>
       </c>
-      <c r="S18" s="8">
-        <v>0</v>
-      </c>
-      <c r="T18" s="8">
+      <c r="S18" s="6">
+        <v>0</v>
+      </c>
+      <c r="T18" s="6">
         <v>3</v>
       </c>
     </row>
@@ -1434,34 +1675,34 @@
       <c r="J19" s="2">
         <v>0</v>
       </c>
-      <c r="K19" s="8">
+      <c r="K19" s="6">
         <v>19</v>
       </c>
-      <c r="L19" s="8">
-        <v>0</v>
-      </c>
-      <c r="M19" s="8">
-        <v>0</v>
-      </c>
-      <c r="N19" s="8">
-        <v>0</v>
-      </c>
-      <c r="O19" s="8">
-        <v>0</v>
-      </c>
-      <c r="P19" s="8">
+      <c r="L19" s="6">
+        <v>0</v>
+      </c>
+      <c r="M19" s="6">
+        <v>0</v>
+      </c>
+      <c r="N19" s="6">
+        <v>0</v>
+      </c>
+      <c r="O19" s="6">
+        <v>0</v>
+      </c>
+      <c r="P19" s="6">
         <v>347</v>
       </c>
-      <c r="Q19" s="8">
-        <v>0</v>
-      </c>
-      <c r="R19" s="8">
-        <v>0</v>
-      </c>
-      <c r="S19" s="8">
-        <v>0</v>
-      </c>
-      <c r="T19" s="8">
+      <c r="Q19" s="6">
+        <v>0</v>
+      </c>
+      <c r="R19" s="6">
+        <v>0</v>
+      </c>
+      <c r="S19" s="6">
+        <v>0</v>
+      </c>
+      <c r="T19" s="6">
         <v>4</v>
       </c>
     </row>
@@ -1478,7 +1719,7 @@
       <c r="D20" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E20" s="12" t="s">
+      <c r="E20" s="9" t="s">
         <v>30</v>
       </c>
       <c r="F20" s="2">
@@ -1490,40 +1731,40 @@
       <c r="H20" s="2">
         <v>289</v>
       </c>
-      <c r="I20" s="12">
+      <c r="I20" s="9">
         <v>0</v>
       </c>
       <c r="J20" s="2">
         <v>0</v>
       </c>
-      <c r="K20" s="8">
-        <v>0</v>
-      </c>
-      <c r="L20" s="8">
+      <c r="K20" s="6">
+        <v>0</v>
+      </c>
+      <c r="L20" s="6">
         <v>1215</v>
       </c>
-      <c r="M20" s="8">
-        <v>0</v>
-      </c>
-      <c r="N20" s="8">
-        <v>0</v>
-      </c>
-      <c r="O20" s="8">
-        <v>0</v>
-      </c>
-      <c r="P20" s="8">
+      <c r="M20" s="6">
+        <v>0</v>
+      </c>
+      <c r="N20" s="6">
+        <v>0</v>
+      </c>
+      <c r="O20" s="6">
+        <v>0</v>
+      </c>
+      <c r="P20" s="6">
         <v>289</v>
       </c>
-      <c r="Q20" s="8">
-        <v>0</v>
-      </c>
-      <c r="R20" s="8">
-        <v>0</v>
-      </c>
-      <c r="S20" s="8">
-        <v>0</v>
-      </c>
-      <c r="T20" s="8">
+      <c r="Q20" s="6">
+        <v>0</v>
+      </c>
+      <c r="R20" s="6">
+        <v>0</v>
+      </c>
+      <c r="S20" s="6">
+        <v>0</v>
+      </c>
+      <c r="T20" s="6">
         <v>5</v>
       </c>
     </row>
@@ -1538,7 +1779,7 @@
         <v>3</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
@@ -1554,34 +1795,34 @@
       <c r="J21" s="2">
         <v>27</v>
       </c>
-      <c r="K21" s="8">
-        <v>0</v>
-      </c>
-      <c r="L21" s="8">
+      <c r="K21" s="6">
+        <v>0</v>
+      </c>
+      <c r="L21" s="6">
         <v>2025</v>
       </c>
-      <c r="M21" s="8">
-        <v>0</v>
-      </c>
-      <c r="N21" s="8">
-        <v>0</v>
-      </c>
-      <c r="O21" s="8">
+      <c r="M21" s="6">
+        <v>0</v>
+      </c>
+      <c r="N21" s="6">
+        <v>0</v>
+      </c>
+      <c r="O21" s="6">
         <v>27</v>
       </c>
-      <c r="P21" s="8">
+      <c r="P21" s="6">
         <v>57</v>
       </c>
-      <c r="Q21" s="8">
-        <v>0</v>
-      </c>
-      <c r="R21" s="8">
+      <c r="Q21" s="6">
+        <v>0</v>
+      </c>
+      <c r="R21" s="6">
         <v>27</v>
       </c>
-      <c r="S21" s="8">
-        <v>0</v>
-      </c>
-      <c r="T21" s="8">
+      <c r="S21" s="6">
+        <v>0</v>
+      </c>
+      <c r="T21" s="6">
         <v>6</v>
       </c>
     </row>
@@ -1596,7 +1837,7 @@
         <v>3</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
@@ -1612,34 +1853,34 @@
       <c r="J22" s="2">
         <v>1282</v>
       </c>
-      <c r="K22" s="8">
+      <c r="K22" s="6">
         <v>905</v>
       </c>
-      <c r="L22" s="8">
+      <c r="L22" s="6">
         <v>3443</v>
       </c>
-      <c r="M22" s="8">
+      <c r="M22" s="6">
         <v>520</v>
       </c>
-      <c r="N22" s="8">
-        <v>0</v>
-      </c>
-      <c r="O22" s="8">
+      <c r="N22" s="6">
+        <v>0</v>
+      </c>
+      <c r="O22" s="6">
         <v>358</v>
       </c>
-      <c r="P22" s="8">
+      <c r="P22" s="6">
         <v>4950</v>
       </c>
-      <c r="Q22" s="8">
+      <c r="Q22" s="6">
         <v>925</v>
       </c>
-      <c r="R22" s="8">
+      <c r="R22" s="6">
         <v>358</v>
       </c>
-      <c r="S22" s="8">
+      <c r="S22" s="6">
         <v>2</v>
       </c>
-      <c r="T22" s="8">
+      <c r="T22" s="6">
         <v>7</v>
       </c>
     </row>
@@ -1654,7 +1895,7 @@
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
-      <c r="T23" s="8">
+      <c r="T23" s="6">
         <v>8</v>
       </c>
     </row>
@@ -1689,34 +1930,34 @@
       <c r="J24" s="2">
         <v>288</v>
       </c>
-      <c r="K24" s="8">
+      <c r="K24" s="6">
         <v>2439</v>
       </c>
-      <c r="L24" s="8">
-        <v>0</v>
-      </c>
-      <c r="M24" s="8">
+      <c r="L24" s="6">
+        <v>0</v>
+      </c>
+      <c r="M24" s="6">
         <v>1669</v>
       </c>
-      <c r="N24" s="8">
-        <v>0</v>
-      </c>
-      <c r="O24" s="8">
+      <c r="N24" s="6">
+        <v>0</v>
+      </c>
+      <c r="O24" s="6">
         <v>5</v>
       </c>
-      <c r="P24" s="8">
+      <c r="P24" s="6">
         <v>14905</v>
       </c>
-      <c r="Q24" s="8">
+      <c r="Q24" s="6">
         <v>282</v>
       </c>
-      <c r="R24" s="8">
+      <c r="R24" s="6">
         <v>5</v>
       </c>
-      <c r="S24" s="8">
+      <c r="S24" s="6">
         <v>6</v>
       </c>
-      <c r="T24" s="8">
+      <c r="T24" s="6">
         <v>1</v>
       </c>
     </row>
@@ -1733,7 +1974,7 @@
       <c r="D25" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E25" s="12" t="s">
+      <c r="E25" s="9" t="s">
         <v>30</v>
       </c>
       <c r="F25" s="2">
@@ -1745,40 +1986,40 @@
       <c r="H25" s="2">
         <v>4481</v>
       </c>
-      <c r="I25" s="12">
+      <c r="I25" s="9">
         <v>783</v>
       </c>
       <c r="J25" s="2">
         <v>783</v>
       </c>
-      <c r="K25" s="8">
+      <c r="K25" s="6">
         <v>13</v>
       </c>
-      <c r="L25" s="8">
+      <c r="L25" s="6">
         <v>945</v>
       </c>
-      <c r="M25" s="8">
+      <c r="M25" s="6">
         <v>950</v>
       </c>
-      <c r="N25" s="8">
-        <v>0</v>
-      </c>
-      <c r="O25" s="8">
-        <v>0</v>
-      </c>
-      <c r="P25" s="8">
+      <c r="N25" s="6">
+        <v>0</v>
+      </c>
+      <c r="O25" s="6">
+        <v>0</v>
+      </c>
+      <c r="P25" s="6">
         <v>2747</v>
       </c>
-      <c r="Q25" s="8">
+      <c r="Q25" s="6">
         <v>783</v>
       </c>
-      <c r="R25" s="8">
-        <v>0</v>
-      </c>
-      <c r="S25" s="8">
+      <c r="R25" s="6">
+        <v>0</v>
+      </c>
+      <c r="S25" s="6">
         <v>1</v>
       </c>
-      <c r="T25" s="8">
+      <c r="T25" s="6">
         <v>2</v>
       </c>
     </row>
@@ -1813,34 +2054,34 @@
       <c r="J26" s="2">
         <v>167</v>
       </c>
-      <c r="K26" s="8">
-        <v>0</v>
-      </c>
-      <c r="L26" s="8">
+      <c r="K26" s="6">
+        <v>0</v>
+      </c>
+      <c r="L26" s="6">
         <v>675</v>
       </c>
-      <c r="M26" s="8">
+      <c r="M26" s="6">
         <v>257</v>
       </c>
-      <c r="N26" s="8">
-        <v>0</v>
-      </c>
-      <c r="O26" s="8">
-        <v>0</v>
-      </c>
-      <c r="P26" s="8">
+      <c r="N26" s="6">
+        <v>0</v>
+      </c>
+      <c r="O26" s="6">
+        <v>0</v>
+      </c>
+      <c r="P26" s="6">
         <v>2349</v>
       </c>
-      <c r="Q26" s="8">
+      <c r="Q26" s="6">
         <v>167</v>
       </c>
-      <c r="R26" s="8">
-        <v>0</v>
-      </c>
-      <c r="S26" s="8">
-        <v>0</v>
-      </c>
-      <c r="T26" s="8">
+      <c r="R26" s="6">
+        <v>0</v>
+      </c>
+      <c r="S26" s="6">
+        <v>0</v>
+      </c>
+      <c r="T26" s="6">
         <v>3</v>
       </c>
     </row>
@@ -1875,34 +2116,34 @@
       <c r="J27" s="2">
         <v>910</v>
       </c>
-      <c r="K27" s="8">
-        <v>0</v>
-      </c>
-      <c r="L27" s="8">
-        <v>0</v>
-      </c>
-      <c r="M27" s="8">
+      <c r="K27" s="6">
+        <v>0</v>
+      </c>
+      <c r="L27" s="6">
+        <v>0</v>
+      </c>
+      <c r="M27" s="6">
         <v>51</v>
       </c>
-      <c r="N27" s="8">
-        <v>0</v>
-      </c>
-      <c r="O27" s="8">
+      <c r="N27" s="6">
+        <v>0</v>
+      </c>
+      <c r="O27" s="6">
         <v>101</v>
       </c>
-      <c r="P27" s="8">
+      <c r="P27" s="6">
         <v>321</v>
       </c>
-      <c r="Q27" s="8">
+      <c r="Q27" s="6">
         <v>809</v>
       </c>
-      <c r="R27" s="8">
+      <c r="R27" s="6">
         <v>101</v>
       </c>
-      <c r="S27" s="8">
-        <v>0</v>
-      </c>
-      <c r="T27" s="8">
+      <c r="S27" s="6">
+        <v>0</v>
+      </c>
+      <c r="T27" s="6">
         <v>4</v>
       </c>
     </row>
@@ -1919,7 +2160,7 @@
       <c r="D28" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E28" s="12" t="s">
+      <c r="E28" s="9" t="s">
         <v>30</v>
       </c>
       <c r="F28" s="2">
@@ -1931,40 +2172,40 @@
       <c r="H28" s="2">
         <v>1293</v>
       </c>
-      <c r="I28" s="12">
+      <c r="I28" s="9">
         <v>1126</v>
       </c>
       <c r="J28" s="2">
         <v>1115</v>
       </c>
-      <c r="K28" s="8">
+      <c r="K28" s="6">
         <v>51</v>
       </c>
-      <c r="L28" s="8">
+      <c r="L28" s="6">
         <v>1013</v>
       </c>
-      <c r="M28" s="8">
+      <c r="M28" s="6">
         <v>13</v>
       </c>
-      <c r="N28" s="8">
-        <v>0</v>
-      </c>
-      <c r="O28" s="8">
+      <c r="N28" s="6">
+        <v>0</v>
+      </c>
+      <c r="O28" s="6">
         <v>11</v>
       </c>
-      <c r="P28" s="8">
+      <c r="P28" s="6">
         <v>154</v>
       </c>
-      <c r="Q28" s="8">
+      <c r="Q28" s="6">
         <v>1104</v>
       </c>
-      <c r="R28" s="8">
+      <c r="R28" s="6">
         <v>11</v>
       </c>
-      <c r="S28" s="8">
-        <v>3</v>
-      </c>
-      <c r="T28" s="8">
+      <c r="S28" s="6">
+        <v>3</v>
+      </c>
+      <c r="T28" s="6">
         <v>5</v>
       </c>
     </row>
@@ -1979,7 +2220,7 @@
         <v>3</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
@@ -1995,34 +2236,34 @@
       <c r="J29" s="2">
         <v>388</v>
       </c>
-      <c r="K29" s="8">
+      <c r="K29" s="6">
         <v>26</v>
       </c>
-      <c r="L29" s="8">
+      <c r="L29" s="6">
         <v>2094</v>
       </c>
-      <c r="M29" s="8">
+      <c r="M29" s="6">
         <v>167</v>
       </c>
-      <c r="N29" s="8">
-        <v>0</v>
-      </c>
-      <c r="O29" s="8">
+      <c r="N29" s="6">
+        <v>0</v>
+      </c>
+      <c r="O29" s="6">
         <v>2</v>
       </c>
-      <c r="P29" s="8">
+      <c r="P29" s="6">
         <v>1145</v>
       </c>
-      <c r="Q29" s="8">
+      <c r="Q29" s="6">
         <v>386</v>
       </c>
-      <c r="R29" s="8">
+      <c r="R29" s="6">
         <v>2</v>
       </c>
-      <c r="S29" s="8">
+      <c r="S29" s="6">
         <v>1</v>
       </c>
-      <c r="T29" s="8">
+      <c r="T29" s="6">
         <v>6</v>
       </c>
     </row>
@@ -2037,7 +2278,7 @@
         <v>3</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
@@ -2053,34 +2294,34 @@
       <c r="J30" s="2">
         <v>3651</v>
       </c>
-      <c r="K30" s="8">
+      <c r="K30" s="6">
         <v>2529</v>
       </c>
-      <c r="L30" s="8">
+      <c r="L30" s="6">
         <v>4727</v>
       </c>
-      <c r="M30" s="8">
+      <c r="M30" s="6">
         <v>3107</v>
       </c>
-      <c r="N30" s="8">
-        <v>0</v>
-      </c>
-      <c r="O30" s="8">
+      <c r="N30" s="6">
+        <v>0</v>
+      </c>
+      <c r="O30" s="6">
         <v>119</v>
       </c>
-      <c r="P30" s="8">
+      <c r="P30" s="6">
         <v>21621</v>
       </c>
-      <c r="Q30" s="8">
+      <c r="Q30" s="6">
         <v>3531</v>
       </c>
-      <c r="R30" s="8">
+      <c r="R30" s="6">
         <v>119</v>
       </c>
-      <c r="S30" s="8">
+      <c r="S30" s="6">
         <v>11</v>
       </c>
-      <c r="T30" s="8">
+      <c r="T30" s="6">
         <v>7</v>
       </c>
     </row>
@@ -2095,7 +2336,7 @@
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
-      <c r="T31" s="8">
+      <c r="T31" s="6">
         <v>8</v>
       </c>
     </row>
@@ -2130,34 +2371,34 @@
       <c r="J32" s="2">
         <v>1205</v>
       </c>
-      <c r="K32" s="8">
+      <c r="K32" s="6">
         <v>1361</v>
       </c>
-      <c r="L32" s="8">
-        <v>0</v>
-      </c>
-      <c r="M32" s="8">
+      <c r="L32" s="6">
+        <v>0</v>
+      </c>
+      <c r="M32" s="6">
         <v>1078</v>
       </c>
-      <c r="N32" s="8">
-        <v>0</v>
-      </c>
-      <c r="O32" s="8">
+      <c r="N32" s="6">
+        <v>0</v>
+      </c>
+      <c r="O32" s="6">
         <v>370</v>
       </c>
-      <c r="P32" s="8">
+      <c r="P32" s="6">
         <v>6830</v>
       </c>
-      <c r="Q32" s="8">
+      <c r="Q32" s="6">
         <v>835</v>
       </c>
-      <c r="R32" s="8">
+      <c r="R32" s="6">
         <v>370</v>
       </c>
-      <c r="S32" s="8">
-        <v>3</v>
-      </c>
-      <c r="T32" s="8">
+      <c r="S32" s="6">
+        <v>3</v>
+      </c>
+      <c r="T32" s="6">
         <v>1</v>
       </c>
     </row>
@@ -2192,34 +2433,34 @@
       <c r="J33" s="2">
         <v>301</v>
       </c>
-      <c r="K33" s="8">
-        <v>0</v>
-      </c>
-      <c r="L33" s="8">
+      <c r="K33" s="6">
+        <v>0</v>
+      </c>
+      <c r="L33" s="6">
         <v>1384</v>
       </c>
-      <c r="M33" s="8">
+      <c r="M33" s="6">
         <v>218</v>
       </c>
-      <c r="N33" s="8">
-        <v>0</v>
-      </c>
-      <c r="O33" s="8">
+      <c r="N33" s="6">
+        <v>0</v>
+      </c>
+      <c r="O33" s="6">
         <v>5</v>
       </c>
-      <c r="P33" s="8">
+      <c r="P33" s="6">
         <v>2747</v>
       </c>
-      <c r="Q33" s="8">
+      <c r="Q33" s="6">
         <v>295</v>
       </c>
-      <c r="R33" s="8">
+      <c r="R33" s="6">
         <v>5</v>
       </c>
-      <c r="S33" s="8">
-        <v>0</v>
-      </c>
-      <c r="T33" s="8">
+      <c r="S33" s="6">
+        <v>0</v>
+      </c>
+      <c r="T33" s="6">
         <v>2</v>
       </c>
     </row>
@@ -2254,34 +2495,34 @@
       <c r="J34" s="2">
         <v>463</v>
       </c>
-      <c r="K34" s="8">
-        <v>0</v>
-      </c>
-      <c r="L34" s="8">
-        <v>0</v>
-      </c>
-      <c r="M34" s="8">
+      <c r="K34" s="6">
+        <v>0</v>
+      </c>
+      <c r="L34" s="6">
+        <v>0</v>
+      </c>
+      <c r="M34" s="6">
         <v>26</v>
       </c>
-      <c r="N34" s="8">
-        <v>0</v>
-      </c>
-      <c r="O34" s="8">
+      <c r="N34" s="6">
+        <v>0</v>
+      </c>
+      <c r="O34" s="6">
         <v>40</v>
       </c>
-      <c r="P34" s="8">
+      <c r="P34" s="6">
         <v>116</v>
       </c>
-      <c r="Q34" s="8">
+      <c r="Q34" s="6">
         <v>424</v>
       </c>
-      <c r="R34" s="8">
+      <c r="R34" s="6">
         <v>40</v>
       </c>
-      <c r="S34" s="8">
-        <v>0</v>
-      </c>
-      <c r="T34" s="8">
+      <c r="S34" s="6">
+        <v>0</v>
+      </c>
+      <c r="T34" s="6">
         <v>3</v>
       </c>
     </row>
@@ -2316,34 +2557,34 @@
       <c r="J35" s="2">
         <v>159</v>
       </c>
-      <c r="K35" s="8">
+      <c r="K35" s="6">
         <v>13</v>
       </c>
-      <c r="L35" s="8">
-        <v>0</v>
-      </c>
-      <c r="M35" s="8">
+      <c r="L35" s="6">
+        <v>0</v>
+      </c>
+      <c r="M35" s="6">
         <v>39</v>
       </c>
-      <c r="N35" s="8">
-        <v>0</v>
-      </c>
-      <c r="O35" s="8">
+      <c r="N35" s="6">
+        <v>0</v>
+      </c>
+      <c r="O35" s="6">
         <v>5</v>
       </c>
-      <c r="P35" s="8">
+      <c r="P35" s="6">
         <v>205</v>
       </c>
-      <c r="Q35" s="8">
+      <c r="Q35" s="6">
         <v>154</v>
       </c>
-      <c r="R35" s="8">
+      <c r="R35" s="6">
         <v>5</v>
       </c>
-      <c r="S35" s="8">
-        <v>0</v>
-      </c>
-      <c r="T35" s="8">
+      <c r="S35" s="6">
+        <v>0</v>
+      </c>
+      <c r="T35" s="6">
         <v>4</v>
       </c>
     </row>
@@ -2378,34 +2619,34 @@
       <c r="J36" s="2">
         <v>66</v>
       </c>
-      <c r="K36" s="8">
-        <v>0</v>
-      </c>
-      <c r="L36" s="8">
-        <v>0</v>
-      </c>
-      <c r="M36" s="8">
+      <c r="K36" s="6">
+        <v>0</v>
+      </c>
+      <c r="L36" s="6">
+        <v>0</v>
+      </c>
+      <c r="M36" s="6">
         <v>13</v>
       </c>
-      <c r="N36" s="8">
-        <v>0</v>
-      </c>
-      <c r="O36" s="8">
+      <c r="N36" s="6">
+        <v>0</v>
+      </c>
+      <c r="O36" s="6">
         <v>2</v>
       </c>
-      <c r="P36" s="8">
+      <c r="P36" s="6">
         <v>270</v>
       </c>
-      <c r="Q36" s="8">
+      <c r="Q36" s="6">
         <v>64</v>
       </c>
-      <c r="R36" s="8">
+      <c r="R36" s="6">
         <v>2</v>
       </c>
-      <c r="S36" s="8">
-        <v>0</v>
-      </c>
-      <c r="T36" s="8">
+      <c r="S36" s="6">
+        <v>0</v>
+      </c>
+      <c r="T36" s="6">
         <v>5</v>
       </c>
     </row>
@@ -2420,7 +2661,7 @@
         <v>3</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
@@ -2436,34 +2677,34 @@
       <c r="J37" s="2">
         <v>77</v>
       </c>
-      <c r="K37" s="8">
+      <c r="K37" s="6">
         <v>34</v>
       </c>
-      <c r="L37" s="8">
+      <c r="L37" s="6">
         <v>4998</v>
       </c>
-      <c r="M37" s="8">
+      <c r="M37" s="6">
         <v>78</v>
       </c>
-      <c r="N37" s="8">
-        <v>0</v>
-      </c>
-      <c r="O37" s="8">
+      <c r="N37" s="6">
+        <v>0</v>
+      </c>
+      <c r="O37" s="6">
         <v>13</v>
       </c>
-      <c r="P37" s="8">
+      <c r="P37" s="6">
         <v>528</v>
       </c>
-      <c r="Q37" s="8">
+      <c r="Q37" s="6">
         <v>64</v>
       </c>
-      <c r="R37" s="8">
+      <c r="R37" s="6">
         <v>13</v>
       </c>
-      <c r="S37" s="8">
-        <v>0</v>
-      </c>
-      <c r="T37" s="8">
+      <c r="S37" s="6">
+        <v>0</v>
+      </c>
+      <c r="T37" s="6">
         <v>6</v>
       </c>
     </row>
@@ -2478,7 +2719,7 @@
         <v>3</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
@@ -2494,39 +2735,39 @@
       <c r="J38" s="2">
         <v>2271</v>
       </c>
-      <c r="K38" s="8">
+      <c r="K38" s="6">
         <v>1408</v>
       </c>
-      <c r="L38" s="8">
+      <c r="L38" s="6">
         <v>6382</v>
       </c>
-      <c r="M38" s="8">
+      <c r="M38" s="6">
         <v>1452</v>
       </c>
-      <c r="N38" s="8">
-        <v>0</v>
-      </c>
-      <c r="O38" s="8">
+      <c r="N38" s="6">
+        <v>0</v>
+      </c>
+      <c r="O38" s="6">
         <v>435</v>
       </c>
-      <c r="P38" s="8">
+      <c r="P38" s="6">
         <v>10696</v>
       </c>
-      <c r="Q38" s="8">
+      <c r="Q38" s="6">
         <v>1836</v>
       </c>
-      <c r="R38" s="8">
+      <c r="R38" s="6">
         <v>435</v>
       </c>
-      <c r="S38" s="8">
-        <v>3</v>
-      </c>
-      <c r="T38" s="8">
+      <c r="S38" s="6">
+        <v>3</v>
+      </c>
+      <c r="T38" s="6">
         <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="T39" s="8">
+      <c r="T39" s="6">
         <v>8</v>
       </c>
     </row>
@@ -2538,134 +2779,139 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:T12"/>
+  <dimension ref="A1:T19"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
-      <c r="M1" s="8"/>
-      <c r="N1" s="8"/>
-      <c r="O1" s="8"/>
-      <c r="P1" s="8"/>
-      <c r="Q1" s="8"/>
-      <c r="R1" s="8"/>
-      <c r="S1" s="8"/>
-      <c r="T1" s="8"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
+      <c r="Q1" s="6"/>
+      <c r="R1" s="6"/>
+      <c r="S1" s="6"/>
+      <c r="T1" s="6"/>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8"/>
-      <c r="N2" s="8"/>
-      <c r="O2" s="8"/>
-      <c r="P2" s="8"/>
-      <c r="Q2" s="8"/>
-      <c r="R2" s="8"/>
-      <c r="S2" s="8"/>
-      <c r="T2" s="8"/>
+        <v>67</v>
+      </c>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
+      <c r="T2" s="6"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>67</v>
+      <c r="A3" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="8"/>
-      <c r="N3" s="8"/>
-      <c r="O3" s="8"/>
-      <c r="P3" s="8"/>
-      <c r="Q3" s="8"/>
-      <c r="R3" s="8"/>
-      <c r="S3" s="8"/>
-      <c r="T3" s="8"/>
+        <v>63</v>
+      </c>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B4" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="8"/>
-      <c r="N4" s="8"/>
-      <c r="O4" s="8"/>
-      <c r="P4" s="8"/>
-      <c r="Q4" s="8"/>
-      <c r="R4" s="8"/>
-      <c r="S4" s="8"/>
-      <c r="T4" s="8"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6"/>
+    </row>
+    <row r="7" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A7" s="27" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="8" spans="1:20" s="4" customFormat="1" ht="131.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="3" t="s">
+      <c r="A8" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="B8" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="E8" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="F8" s="13" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="D8" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="E8" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="F8" s="30" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>3</v>
       </c>
@@ -2685,7 +2931,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>3</v>
       </c>
@@ -2705,7 +2951,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>3</v>
       </c>
@@ -2725,7 +2971,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>3</v>
       </c>
@@ -2745,9 +2991,98 @@
         <v>9</v>
       </c>
     </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B15" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="32" t="s">
+        <v>85</v>
+      </c>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>3</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="31" t="s">
+        <v>81</v>
+      </c>
+      <c r="E16" s="31"/>
+      <c r="F16" s="31"/>
+      <c r="G16" s="31"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>3</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" s="31" t="s">
+        <v>83</v>
+      </c>
+      <c r="E17" s="31"/>
+      <c r="F17" s="31"/>
+      <c r="G17" s="31"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>3</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="31" t="s">
+        <v>82</v>
+      </c>
+      <c r="E18" s="31"/>
+      <c r="F18" s="31"/>
+      <c r="G18" s="31"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>3</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" s="31" t="s">
+        <v>84</v>
+      </c>
+      <c r="E19" s="31"/>
+      <c r="F19" s="31"/>
+      <c r="G19" s="31"/>
+    </row>
   </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="D16:G16"/>
+    <mergeCell ref="D18:G18"/>
+    <mergeCell ref="D17:G17"/>
+    <mergeCell ref="D19:G19"/>
+    <mergeCell ref="D15:G15"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2757,11 +3092,13 @@
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="8.85546875" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="6" width="11" hidden="1" customWidth="1"/>
+    <col min="7" max="9" width="7.140625" customWidth="1"/>
+    <col min="10" max="11" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -2769,98 +3106,98 @@
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="E5" t="s">
+    <row r="5" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A5" s="27" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" s="4" customFormat="1" ht="119.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="G6" s="28" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" s="4" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" s="3" t="s">
+      <c r="H6" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="I6" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="13">
+        <v>3</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="13">
+        <v>20</v>
+      </c>
+      <c r="F7" s="13">
+        <v>16</v>
+      </c>
+      <c r="G7" s="13">
+        <v>80</v>
+      </c>
+      <c r="H7" s="13">
         <v>60</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="2">
-        <v>3</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" s="2">
+      <c r="I7" s="15">
         <v>20</v>
       </c>
-      <c r="F7" s="2">
-        <v>16</v>
-      </c>
-      <c r="G7" s="2">
-        <v>80</v>
-      </c>
-      <c r="H7" s="2">
-        <v>60</v>
-      </c>
-      <c r="I7" s="12">
-        <v>20</v>
-      </c>
-      <c r="J7" s="2">
+      <c r="J7" s="10">
         <v>12</v>
       </c>
       <c r="K7" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+    <row r="8" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="25" t="s">
         <v>28</v>
       </c>
       <c r="B8" s="5" t="s">
@@ -2884,18 +3221,18 @@
       <c r="H8" s="2">
         <v>25</v>
       </c>
-      <c r="I8" s="2">
+      <c r="I8" s="17">
         <v>15</v>
       </c>
-      <c r="J8" s="2">
+      <c r="J8" s="10">
         <v>5</v>
       </c>
       <c r="K8" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+    <row r="9" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="25" t="s">
         <v>28</v>
       </c>
       <c r="B9" s="5" t="s">
@@ -2919,18 +3256,18 @@
       <c r="H9" s="2">
         <v>100</v>
       </c>
-      <c r="I9" s="2">
+      <c r="I9" s="17">
         <v>70</v>
       </c>
-      <c r="J9" s="2">
+      <c r="J9" s="10">
         <v>20</v>
       </c>
       <c r="K9" s="2">
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+    <row r="10" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="25" t="s">
         <v>28</v>
       </c>
       <c r="B10" s="5" t="s">
@@ -2954,18 +3291,18 @@
       <c r="H10" s="2">
         <v>0</v>
       </c>
-      <c r="I10" s="2">
-        <v>0</v>
-      </c>
-      <c r="J10" s="2">
+      <c r="I10" s="17">
+        <v>0</v>
+      </c>
+      <c r="J10" s="10">
         <v>0</v>
       </c>
       <c r="K10" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+    <row r="11" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="25" t="s">
         <v>28</v>
       </c>
       <c r="B11" s="5" t="s">
@@ -2989,31 +3326,31 @@
       <c r="H11" s="2">
         <v>45</v>
       </c>
-      <c r="I11" s="2">
-        <v>0</v>
-      </c>
-      <c r="J11" s="2">
+      <c r="I11" s="17">
+        <v>0</v>
+      </c>
+      <c r="J11" s="10">
         <v>9</v>
       </c>
       <c r="K11" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
+    <row r="12" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="16"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="2"/>
+    </row>
+    <row r="13" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="25" t="s">
         <v>28</v>
       </c>
       <c r="B13" s="2" t="s">
@@ -3022,7 +3359,7 @@
       <c r="C13" s="2">
         <v>3</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="9" t="s">
         <v>30</v>
       </c>
       <c r="E13" s="2">
@@ -3037,18 +3374,18 @@
       <c r="H13" s="2">
         <v>70</v>
       </c>
-      <c r="I13" s="12">
+      <c r="I13" s="18">
         <v>55</v>
       </c>
-      <c r="J13" s="2">
+      <c r="J13" s="10">
         <v>14</v>
       </c>
       <c r="K13" s="2">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
+    <row r="14" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="25" t="s">
         <v>28</v>
       </c>
       <c r="B14" s="2" t="s">
@@ -3072,18 +3409,18 @@
       <c r="H14" s="2">
         <v>45</v>
       </c>
-      <c r="I14" s="2">
+      <c r="I14" s="17">
         <v>25</v>
       </c>
-      <c r="J14" s="2">
+      <c r="J14" s="10">
         <v>9</v>
       </c>
       <c r="K14" s="2">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
+    <row r="15" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="25" t="s">
         <v>28</v>
       </c>
       <c r="B15" s="2" t="s">
@@ -3107,18 +3444,18 @@
       <c r="H15" s="2">
         <v>100</v>
       </c>
-      <c r="I15" s="2">
+      <c r="I15" s="17">
         <v>100</v>
       </c>
-      <c r="J15" s="2">
+      <c r="J15" s="10">
         <v>20</v>
       </c>
       <c r="K15" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
+    <row r="16" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="25" t="s">
         <v>28</v>
       </c>
       <c r="B16" s="2" t="s">
@@ -3142,101 +3479,101 @@
       <c r="H16" s="2">
         <v>0</v>
       </c>
-      <c r="I16" s="2">
-        <v>0</v>
-      </c>
-      <c r="J16" s="2">
+      <c r="I16" s="17">
+        <v>0</v>
+      </c>
+      <c r="J16" s="10">
         <v>0</v>
       </c>
       <c r="K16" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
+    <row r="17" spans="1:11" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="C17" s="2">
-        <v>3</v>
-      </c>
-      <c r="D17" s="2" t="s">
+      <c r="C17" s="20">
+        <v>3</v>
+      </c>
+      <c r="D17" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="E17" s="2">
+      <c r="E17" s="20">
         <v>20</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="20">
         <v>6</v>
       </c>
-      <c r="G17" s="2">
-        <v>30</v>
-      </c>
-      <c r="H17" s="2">
-        <v>30</v>
-      </c>
-      <c r="I17" s="2">
+      <c r="G17" s="20">
+        <v>30</v>
+      </c>
+      <c r="H17" s="20">
+        <v>30</v>
+      </c>
+      <c r="I17" s="21">
         <v>10</v>
       </c>
-      <c r="J17" s="2">
+      <c r="J17" s="10">
         <v>6</v>
       </c>
       <c r="K17" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+    <row r="18" spans="1:11" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="23"/>
+      <c r="B18" s="23"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="23"/>
+      <c r="H18" s="23"/>
+      <c r="I18" s="23"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+    </row>
+    <row r="19" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C19" s="2">
-        <v>3</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="E19" s="2">
-        <v>30</v>
-      </c>
-      <c r="F19" s="2">
+      <c r="C19" s="13">
+        <v>3</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" s="13">
+        <v>30</v>
+      </c>
+      <c r="F19" s="13">
         <v>24</v>
       </c>
-      <c r="G19" s="2">
+      <c r="G19" s="13">
         <v>80</v>
       </c>
-      <c r="H19" s="2">
+      <c r="H19" s="13">
         <v>73.3</v>
       </c>
-      <c r="I19" s="12">
+      <c r="I19" s="15">
         <v>40</v>
       </c>
-      <c r="J19" s="2">
+      <c r="J19" s="10">
         <v>22</v>
       </c>
       <c r="K19" s="2">
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
+    <row r="20" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="16" t="s">
         <v>47</v>
       </c>
       <c r="B20" s="5" t="s">
@@ -3260,18 +3597,18 @@
       <c r="H20" s="2">
         <v>56.7</v>
       </c>
-      <c r="I20" s="2">
+      <c r="I20" s="17">
         <v>46.7</v>
       </c>
-      <c r="J20" s="2">
+      <c r="J20" s="10">
         <v>17</v>
       </c>
       <c r="K20" s="2">
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
+    <row r="21" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="16" t="s">
         <v>47</v>
       </c>
       <c r="B21" s="5" t="s">
@@ -3295,18 +3632,18 @@
       <c r="H21" s="2">
         <v>100</v>
       </c>
-      <c r="I21" s="2">
+      <c r="I21" s="17">
         <v>70</v>
       </c>
-      <c r="J21" s="2">
+      <c r="J21" s="10">
         <v>30</v>
       </c>
       <c r="K21" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
+    <row r="22" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="16" t="s">
         <v>47</v>
       </c>
       <c r="B22" s="5" t="s">
@@ -3330,18 +3667,18 @@
       <c r="H22" s="2">
         <v>0</v>
       </c>
-      <c r="I22" s="2">
-        <v>0</v>
-      </c>
-      <c r="J22" s="2">
+      <c r="I22" s="17">
+        <v>0</v>
+      </c>
+      <c r="J22" s="10">
         <v>0</v>
       </c>
       <c r="K22" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
+    <row r="23" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="16" t="s">
         <v>47</v>
       </c>
       <c r="B23" s="5" t="s">
@@ -3365,31 +3702,31 @@
       <c r="H23" s="2">
         <v>60</v>
       </c>
-      <c r="I23" s="2">
+      <c r="I23" s="17">
         <v>16.7</v>
       </c>
-      <c r="J23" s="2">
+      <c r="J23" s="10">
         <v>18</v>
       </c>
       <c r="K23" s="2">
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6"/>
-      <c r="K24" s="6"/>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
+    <row r="24" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="16"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="17"/>
+      <c r="J24" s="10"/>
+      <c r="K24" s="2"/>
+    </row>
+    <row r="25" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="16" t="s">
         <v>47</v>
       </c>
       <c r="B25" s="2" t="s">
@@ -3398,7 +3735,7 @@
       <c r="C25" s="2">
         <v>3</v>
       </c>
-      <c r="D25" s="12" t="s">
+      <c r="D25" s="9" t="s">
         <v>30</v>
       </c>
       <c r="E25" s="2">
@@ -3413,18 +3750,18 @@
       <c r="H25" s="2">
         <v>73.3</v>
       </c>
-      <c r="I25" s="12">
+      <c r="I25" s="18">
         <v>20</v>
       </c>
-      <c r="J25" s="2">
+      <c r="J25" s="10">
         <v>22</v>
       </c>
       <c r="K25" s="2">
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
+    <row r="26" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="16" t="s">
         <v>47</v>
       </c>
       <c r="B26" s="2" t="s">
@@ -3448,18 +3785,18 @@
       <c r="H26" s="2">
         <v>36.700000000000003</v>
       </c>
-      <c r="I26" s="2">
+      <c r="I26" s="17">
         <v>26.7</v>
       </c>
-      <c r="J26" s="2">
+      <c r="J26" s="10">
         <v>11</v>
       </c>
       <c r="K26" s="2">
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
+    <row r="27" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="16" t="s">
         <v>47</v>
       </c>
       <c r="B27" s="2" t="s">
@@ -3483,18 +3820,18 @@
       <c r="H27" s="2">
         <v>100</v>
       </c>
-      <c r="I27" s="2">
+      <c r="I27" s="17">
         <v>100</v>
       </c>
-      <c r="J27" s="2">
+      <c r="J27" s="10">
         <v>30</v>
       </c>
       <c r="K27" s="2">
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
+    <row r="28" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="16" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="2" t="s">
@@ -3518,45 +3855,45 @@
       <c r="H28" s="2">
         <v>3.3</v>
       </c>
-      <c r="I28" s="2">
-        <v>0</v>
-      </c>
-      <c r="J28" s="2">
+      <c r="I28" s="17">
+        <v>0</v>
+      </c>
+      <c r="J28" s="10">
         <v>1</v>
       </c>
       <c r="K28" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
+    <row r="29" spans="1:11" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="C29" s="2">
-        <v>3</v>
-      </c>
-      <c r="D29" s="2" t="s">
+      <c r="C29" s="20">
+        <v>3</v>
+      </c>
+      <c r="D29" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="E29" s="2">
-        <v>30</v>
-      </c>
-      <c r="F29" s="2">
+      <c r="E29" s="20">
+        <v>30</v>
+      </c>
+      <c r="F29" s="20">
         <v>20</v>
       </c>
-      <c r="G29" s="2">
+      <c r="G29" s="20">
         <v>66.7</v>
       </c>
-      <c r="H29" s="2">
+      <c r="H29" s="20">
         <v>63.3</v>
       </c>
-      <c r="I29" s="2">
-        <v>30</v>
-      </c>
-      <c r="J29" s="2">
+      <c r="I29" s="21">
+        <v>30</v>
+      </c>
+      <c r="J29" s="10">
         <v>19</v>
       </c>
       <c r="K29" s="2">
@@ -3565,7 +3902,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
